--- a/MAIN/Input Excel Sheets/Trade Study Inputs/ASEN4138_Config_Jet_FW_Trade.xlsx
+++ b/MAIN/Input Excel Sheets/Trade Study Inputs/ASEN4138_Config_Jet_FW_Trade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Input Excel Sheets\Trade Study Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE9A0C1-4BA5-49B5-939F-735CDB3B7A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F9B6F0-6D15-484A-9E09-23681B834739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F2" s="7">
         <f>2*N2/((1+Q2)*(P2*N2)^(1/2))</f>
-        <v>33.782975558492971</v>
+        <v>28.551825530649818</v>
       </c>
       <c r="G2" s="7">
         <v>4</v>
       </c>
       <c r="H2" s="7">
         <f>F2/G2</f>
-        <v>8.4457438896232429</v>
+        <v>7.1379563826624546</v>
       </c>
       <c r="I2" s="7">
         <v>14</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="K2" s="7">
         <f>G2*3.1415*F2/2</f>
-        <v>212.25843543401135</v>
+        <v>179.39111980907282</v>
       </c>
       <c r="L2" s="7">
         <v>1</v>
@@ -3994,18 +3994,18 @@
         <v>1300</v>
       </c>
       <c r="P2" s="7">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" s="7">
         <v>0.35</v>
       </c>
       <c r="R2" s="7">
-        <f t="shared" ref="R2:R11" si="1">ATAN(-TAN(0*3.1415/180)+(4*(1-Q2))/((1+Q2)*P2))*180/3.1415</f>
-        <v>57.01656009152628</v>
+        <f t="shared" ref="R2:R10" si="1">ATAN(-TAN(0*3.1415/180)+(4*(1-Q2))/((1+Q2)*P2))*180/3.1415</f>
+        <v>47.741432696265761</v>
       </c>
       <c r="S2" s="7">
         <f>ATAN(TAN(R2*3.1415/180)+(Q2-1)/((1+Q2)*P2))*180/3.1415</f>
-        <v>49.129040643377273</v>
+        <v>39.537323243389167</v>
       </c>
       <c r="T2" s="7">
         <v>1.1000000000000001</v>
@@ -4054,11 +4054,11 @@
       </c>
       <c r="AI2" s="7">
         <f>(2/3)*P2*N2*(1+Q2)*0.06</f>
-        <v>43.875</v>
+        <v>61.424999999999997</v>
       </c>
       <c r="AJ2" s="7">
         <f t="shared" ref="AJ2:AJ11" si="2">2*AI2</f>
-        <v>87.75</v>
+        <v>122.85</v>
       </c>
       <c r="AK2" s="7">
         <v>1.8</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AN2" s="7">
         <f t="shared" ref="AN2:AN11" si="3">(2/3)*((2*AI2)/((SQRT(AK2*AI2))*(1+AL2)))*(1+AL2+AL2^2)/(1+AL2)</f>
-        <v>5.2393761133818257</v>
+        <v>6.1993134200866535</v>
       </c>
       <c r="AO2" s="7">
         <v>1.1000000000000001</v>
@@ -4116,14 +4116,14 @@
       </c>
       <c r="F3" s="7">
         <f t="shared" ref="F3:F11" si="4">2*N3/((1+Q3)*(P3*N3)^(1/2))</f>
-        <v>32.457633037343172</v>
+        <v>27.431706659927453</v>
       </c>
       <c r="G3" s="7">
         <v>4</v>
       </c>
       <c r="H3" s="7">
         <f t="shared" ref="H3:H11" si="5">F3/G3</f>
-        <v>8.1144082593357929</v>
+        <v>6.8579266649818633</v>
       </c>
       <c r="I3" s="7">
         <v>14</v>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="K3" s="7">
         <f t="shared" ref="K3:K11" si="6">G3*3.1415*F3/2</f>
-        <v>203.93130837362716</v>
+        <v>172.35341294432419</v>
       </c>
       <c r="L3" s="7">
         <v>1</v>
@@ -4149,18 +4149,18 @@
         <v>1200</v>
       </c>
       <c r="P3" s="7">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" s="7">
         <v>0.35</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" si="1"/>
-        <v>57.01656009152628</v>
+        <v>47.741432696265761</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" ref="S3:S11" si="7">ATAN(TAN(R3*3.1415/180)+(Q3-1)/((1+Q3)*P3))*180/3.1415</f>
-        <v>49.129040643377273</v>
+        <v>39.537323243389167</v>
       </c>
       <c r="T3" s="7">
         <v>1.1000000000000001</v>
@@ -4209,11 +4209,11 @@
       </c>
       <c r="AI3" s="7">
         <f t="shared" ref="AI3:AI11" si="8">(2/3)*P3*N3*(1+Q3)*0.06</f>
-        <v>40.5</v>
+        <v>56.699999999999989</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="2"/>
-        <v>81</v>
+        <v>113.39999999999998</v>
       </c>
       <c r="AK3" s="7">
         <v>1.8</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AN3" s="7">
         <f t="shared" si="3"/>
-        <v>5.0338297447578277</v>
+        <v>5.9561076769054582</v>
       </c>
       <c r="AO3" s="7">
         <v>1.1000000000000001</v>
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F4" s="7">
         <f t="shared" si="4"/>
-        <v>31.075817723560039</v>
+        <v>26.263859568234611</v>
       </c>
       <c r="G4" s="7">
         <v>4</v>
       </c>
       <c r="H4" s="7">
         <f t="shared" si="5"/>
-        <v>7.7689544308900098</v>
+        <v>6.5659648920586529</v>
       </c>
       <c r="I4" s="7">
         <v>14</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K4" s="7">
         <f t="shared" si="6"/>
-        <v>195.24936275712773</v>
+        <v>165.01582966721807</v>
       </c>
       <c r="L4" s="7">
         <v>1</v>
@@ -4304,18 +4304,18 @@
         <v>1100</v>
       </c>
       <c r="P4" s="7">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" s="7">
         <v>0.35</v>
       </c>
       <c r="R4" s="7">
         <f t="shared" si="1"/>
-        <v>57.01656009152628</v>
+        <v>47.741432696265761</v>
       </c>
       <c r="S4" s="7">
         <f t="shared" si="7"/>
-        <v>49.129040643377273</v>
+        <v>39.537323243389167</v>
       </c>
       <c r="T4" s="7">
         <v>1.1000000000000001</v>
@@ -4364,11 +4364,11 @@
       </c>
       <c r="AI4" s="7">
         <f t="shared" si="8"/>
-        <v>37.125</v>
+        <v>51.975000000000001</v>
       </c>
       <c r="AJ4" s="7">
         <f t="shared" si="2"/>
-        <v>74.25</v>
+        <v>103.95</v>
       </c>
       <c r="AK4" s="7">
         <v>1.8</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="AN4" s="7">
         <f t="shared" si="3"/>
-        <v>4.8195250534613132</v>
+        <v>5.702538946584915</v>
       </c>
       <c r="AO4" s="7">
         <v>1.1000000000000001</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="F5" s="7">
         <f t="shared" si="4"/>
-        <v>29.62962962962963</v>
+        <v>25.041607547511603</v>
       </c>
       <c r="G5" s="7">
         <v>4</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" si="5"/>
-        <v>7.4074074074074074</v>
+        <v>6.2604018868779008</v>
       </c>
       <c r="I5" s="7">
         <v>14</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="K5" s="7">
         <f t="shared" si="6"/>
-        <v>186.16296296296298</v>
+        <v>157.3364202210154</v>
       </c>
       <c r="L5" s="7">
         <v>1</v>
@@ -4459,18 +4459,18 @@
         <v>1000</v>
       </c>
       <c r="P5" s="7">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" s="7">
         <v>0.35</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" si="1"/>
-        <v>57.01656009152628</v>
+        <v>47.741432696265761</v>
       </c>
       <c r="S5" s="7">
         <f t="shared" si="7"/>
-        <v>49.129040643377273</v>
+        <v>39.537323243389167</v>
       </c>
       <c r="T5" s="7">
         <v>1.1000000000000001</v>
@@ -4519,11 +4519,11 @@
       </c>
       <c r="AI5" s="7">
         <f t="shared" si="8"/>
-        <v>33.75</v>
+        <v>47.25</v>
       </c>
       <c r="AJ5" s="7">
         <f t="shared" si="2"/>
-        <v>67.5</v>
+        <v>94.5</v>
       </c>
       <c r="AK5" s="7">
         <v>1.8</v>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AN5" s="7">
         <f t="shared" si="3"/>
-        <v>4.595236836407226</v>
+        <v>5.4371575492846853</v>
       </c>
       <c r="AO5" s="7">
         <v>1.1000000000000001</v>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="F6" s="7">
         <f t="shared" si="4"/>
-        <v>28.109134757052264</v>
+        <v>23.756554836659941</v>
       </c>
       <c r="G6" s="7">
         <v>4</v>
       </c>
       <c r="H6" s="7">
         <f t="shared" si="5"/>
-        <v>7.0272836892630659</v>
+        <v>5.9391387091649852</v>
       </c>
       <c r="I6" s="7">
         <v>14</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K6" s="7">
         <f t="shared" si="6"/>
-        <v>176.60969367855938</v>
+        <v>149.26243403873443</v>
       </c>
       <c r="L6" s="7">
         <v>1</v>
@@ -4614,18 +4614,18 @@
         <v>900</v>
       </c>
       <c r="P6" s="7">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" s="7">
         <v>0.35</v>
       </c>
       <c r="R6" s="7">
         <f t="shared" si="1"/>
-        <v>57.01656009152628</v>
+        <v>47.741432696265761</v>
       </c>
       <c r="S6" s="7">
         <f t="shared" si="7"/>
-        <v>49.129040643377273</v>
+        <v>39.537323243389167</v>
       </c>
       <c r="T6" s="7">
         <v>1.1000000000000001</v>
@@ -4674,11 +4674,11 @@
       </c>
       <c r="AI6" s="7">
         <f t="shared" si="8"/>
-        <v>30.374999999999996</v>
+        <v>42.524999999999991</v>
       </c>
       <c r="AJ6" s="7">
         <f t="shared" si="2"/>
-        <v>60.749999999999993</v>
+        <v>85.049999999999983</v>
       </c>
       <c r="AK6" s="7">
         <v>1.8</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AN6" s="7">
         <f t="shared" si="3"/>
-        <v>4.359424437286016</v>
+        <v>5.1581405558756437</v>
       </c>
       <c r="AO6" s="7">
         <v>1.1000000000000001</v>
@@ -4736,14 +4736,14 @@
       </c>
       <c r="F7" s="7">
         <f t="shared" si="4"/>
-        <v>23.888171106069777</v>
+        <v>26.707787225659178</v>
       </c>
       <c r="G7" s="7">
         <v>4</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="5"/>
-        <v>5.9720427765174442</v>
+        <v>6.6769468064147945</v>
       </c>
       <c r="I7" s="7">
         <v>14</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="K7" s="7">
         <f t="shared" si="6"/>
-        <v>150.08937905943642</v>
+        <v>167.80502713881663</v>
       </c>
       <c r="L7" s="7">
         <v>1</v>
@@ -4769,18 +4769,18 @@
         <v>1300</v>
       </c>
       <c r="P7" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="7">
         <v>0.35</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="1"/>
-        <v>37.610700026299568</v>
+        <v>43.920371137240153</v>
       </c>
       <c r="S7" s="7">
         <f t="shared" si="7"/>
-        <v>30.019252772031148</v>
+        <v>35.838709929352603</v>
       </c>
       <c r="T7" s="7">
         <v>1.1000000000000001</v>
@@ -4829,11 +4829,11 @@
       </c>
       <c r="AI7" s="7">
         <f t="shared" si="8"/>
-        <v>87.75</v>
+        <v>70.2</v>
       </c>
       <c r="AJ7" s="7">
         <f t="shared" si="2"/>
-        <v>175.5</v>
+        <v>140.4</v>
       </c>
       <c r="AK7" s="7">
         <v>1.8</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="AN7" s="7">
         <f t="shared" si="3"/>
-        <v>7.409596757918214</v>
+        <v>6.6273448146268725</v>
       </c>
       <c r="AO7" s="7">
         <v>1.1000000000000001</v>
@@ -4891,14 +4891,14 @@
       </c>
       <c r="F8" s="7">
         <f t="shared" si="4"/>
-        <v>22.951012421969878</v>
+        <v>25.660011963983361</v>
       </c>
       <c r="G8" s="7">
         <v>4</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="5"/>
-        <v>5.7377531054924695</v>
+        <v>6.4150029909958404</v>
       </c>
       <c r="I8" s="7">
         <v>14</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="K8" s="7">
         <f t="shared" si="6"/>
-        <v>144.20121104723674</v>
+        <v>161.22185516970748</v>
       </c>
       <c r="L8" s="7">
         <v>1</v>
@@ -4924,18 +4924,18 @@
         <v>1200</v>
       </c>
       <c r="P8" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="7">
         <v>0.35</v>
       </c>
       <c r="R8" s="7">
         <f t="shared" si="1"/>
-        <v>37.610700026299568</v>
+        <v>43.920371137240153</v>
       </c>
       <c r="S8" s="7">
         <f t="shared" si="7"/>
-        <v>30.019252772031148</v>
+        <v>35.838709929352603</v>
       </c>
       <c r="T8" s="7">
         <v>1.1000000000000001</v>
@@ -4984,11 +4984,11 @@
       </c>
       <c r="AI8" s="7">
         <f t="shared" si="8"/>
-        <v>81</v>
+        <v>64.8</v>
       </c>
       <c r="AJ8" s="7">
         <f t="shared" si="2"/>
-        <v>162</v>
+        <v>129.6</v>
       </c>
       <c r="AK8" s="7">
         <v>1.8</v>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="3"/>
-        <v>7.1189102957136177</v>
+        <v>6.3673469387755093</v>
       </c>
       <c r="AO8" s="7">
         <v>1.1000000000000001</v>
@@ -5046,14 +5046,14 @@
       </c>
       <c r="F9" s="7">
         <f t="shared" si="4"/>
-        <v>21.973921443246407</v>
+        <v>24.567591039669626</v>
       </c>
       <c r="G9" s="7">
         <v>4</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="5"/>
-        <v>5.4934803608116018</v>
+        <v>6.1418977599174065</v>
       </c>
       <c r="I9" s="7">
         <v>14</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="K9" s="7">
         <f t="shared" si="6"/>
-        <v>138.06214842791718</v>
+        <v>154.35817450224428</v>
       </c>
       <c r="L9" s="7">
         <v>1</v>
@@ -5079,18 +5079,18 @@
         <v>1100</v>
       </c>
       <c r="P9" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="7">
         <v>0.35</v>
       </c>
       <c r="R9" s="7">
         <f t="shared" si="1"/>
-        <v>37.610700026299568</v>
+        <v>43.920371137240153</v>
       </c>
       <c r="S9" s="7">
         <f t="shared" si="7"/>
-        <v>30.019252772031148</v>
+        <v>35.838709929352603</v>
       </c>
       <c r="T9" s="7">
         <v>1.1000000000000001</v>
@@ -5139,11 +5139,11 @@
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="8"/>
-        <v>74.25</v>
+        <v>59.4</v>
       </c>
       <c r="AJ9" s="7">
         <f t="shared" si="2"/>
-        <v>148.5</v>
+        <v>118.8</v>
       </c>
       <c r="AK9" s="7">
         <v>1.8</v>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="3"/>
-        <v>6.815837694801905</v>
+        <v>6.0962705636730101</v>
       </c>
       <c r="AO9" s="7">
         <v>1.1000000000000001</v>
@@ -5201,14 +5201,14 @@
       </c>
       <c r="F10" s="7">
         <f t="shared" si="4"/>
-        <v>20.951312035156963</v>
+        <v>23.424278964210217</v>
       </c>
       <c r="G10" s="7">
         <v>4</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="5"/>
-        <v>5.2378280087892408</v>
+        <v>5.8560697410525542</v>
       </c>
       <c r="I10" s="7">
         <v>14</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="K10" s="7">
         <f t="shared" si="6"/>
-        <v>131.63709351689121</v>
+        <v>147.17474473213281</v>
       </c>
       <c r="L10" s="7">
         <v>1</v>
@@ -5234,18 +5234,18 @@
         <v>1000</v>
       </c>
       <c r="P10" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="7">
         <v>0.35</v>
       </c>
       <c r="R10" s="7">
         <f t="shared" si="1"/>
-        <v>37.610700026299568</v>
+        <v>43.920371137240153</v>
       </c>
       <c r="S10" s="7">
         <f t="shared" si="7"/>
-        <v>30.019252772031148</v>
+        <v>35.838709929352603</v>
       </c>
       <c r="T10" s="7">
         <v>1.1000000000000001</v>
@@ -5294,11 +5294,11 @@
       </c>
       <c r="AI10" s="7">
         <f t="shared" si="8"/>
-        <v>67.5</v>
+        <v>54</v>
       </c>
       <c r="AJ10" s="7">
         <f t="shared" si="2"/>
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="AK10" s="7">
         <v>1.8</v>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="AN10" s="7">
         <f t="shared" si="3"/>
-        <v>6.4986462563635357</v>
+        <v>5.812565916381355</v>
       </c>
       <c r="AO10" s="7">
         <v>1.1000000000000001</v>
@@ -5356,14 +5356,14 @@
       </c>
       <c r="F11" s="7">
         <f t="shared" si="4"/>
-        <v>19.876159799998131</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="G11" s="7">
         <v>4</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="5"/>
-        <v>4.9690399499995328</v>
+        <v>5.5555555555555554</v>
       </c>
       <c r="I11" s="7">
         <v>14</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="K11" s="7">
         <f t="shared" si="6"/>
-        <v>124.88191202338827</v>
+        <v>139.62222222222223</v>
       </c>
       <c r="L11" s="7">
         <v>1</v>
@@ -5389,18 +5389,18 @@
         <v>900</v>
       </c>
       <c r="P11" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="7">
         <v>0.35</v>
       </c>
       <c r="R11" s="7">
         <f>ATAN(-TAN(0*3.1415/180)+(4*(1-Q11))/((1+Q11)*P11))*180/3.1415</f>
-        <v>37.610700026299568</v>
+        <v>43.920371137240153</v>
       </c>
       <c r="S11" s="7">
         <f t="shared" si="7"/>
-        <v>30.019252772031148</v>
+        <v>35.838709929352603</v>
       </c>
       <c r="T11" s="7">
         <v>1.1000000000000001</v>
@@ -5449,11 +5449,11 @@
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="8"/>
-        <v>60.749999999999993</v>
+        <v>48.6</v>
       </c>
       <c r="AJ11" s="7">
         <f t="shared" si="2"/>
-        <v>121.49999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AK11" s="7">
         <v>1.8</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="3"/>
-        <v>6.1651571633505835</v>
+        <v>5.5142842036886703</v>
       </c>
       <c r="AO11" s="7">
         <v>1.1000000000000001</v>
